--- a/artfynd/A 8714-2026 artfynd.xlsx
+++ b/artfynd/A 8714-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110633253</v>
+        <v>110633567</v>
       </c>
       <c r="B2" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484838.5499820957</v>
+        <v>484919</v>
       </c>
       <c r="R2" t="n">
-        <v>6721391.662678228</v>
+        <v>6721367</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +747,9 @@
           <t>2023-07-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,12 +774,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Brandstubbe</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,16 +800,11 @@
         <v>110632930</v>
       </c>
       <c r="B3" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -854,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484944.607288576</v>
+        <v>484945</v>
       </c>
       <c r="R3" t="n">
-        <v>6721364.226356026</v>
+        <v>6721364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,19 +868,9 @@
           <t>2023-07-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -952,37 +923,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110632958</v>
+        <v>110633009</v>
       </c>
       <c r="B4" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -995,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484707.713585832</v>
+        <v>484708</v>
       </c>
       <c r="R4" t="n">
-        <v>6721371.114490658</v>
+        <v>6721371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,19 +994,9 @@
           <t>2023-07-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,27 +1016,27 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Nordsluttning med oskött barrskog mest gran och ett stort inslag med asp och sälg</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Torr</t>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Populus tremula # Torr</t>
+          <t>Pinus sylvestris # På tallstam</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1098,19 +1054,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110633009</v>
+        <v>110633161</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1141,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484707.713585832</v>
+        <v>484876</v>
       </c>
       <c r="R5" t="n">
-        <v>6721371.114490658</v>
+        <v>6721369</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1174,19 +1125,9 @@
           <t>2023-07-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1206,27 +1147,22 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Oskött barrblandskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # På tallstam</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1247,12 +1183,7 @@
         <v>110633238</v>
       </c>
       <c r="B6" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,10 +1218,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484838.5499820957</v>
+        <v>484838</v>
       </c>
       <c r="R6" t="n">
-        <v>6721391.662678228</v>
+        <v>6721392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1320,19 +1251,9 @@
           <t>2023-07-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1380,15 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110633161</v>
+        <v>110632958</v>
       </c>
       <c r="B7" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1423,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484875.81334458</v>
+        <v>484708</v>
       </c>
       <c r="R7" t="n">
-        <v>6721369.422367026</v>
+        <v>6721371</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1456,19 +1372,9 @@
           <t>2023-07-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1488,22 +1394,27 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Oskött barrblandskog</t>
+          <t>Nordsluttning med oskött barrskog mest gran och ett stort inslag med asp och sälg</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Torr</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula # Torr</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1521,43 +1432,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110633567</v>
+        <v>110633540</v>
       </c>
       <c r="B8" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1565,10 +1472,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484918.5663425042</v>
+        <v>484830</v>
       </c>
       <c r="R8" t="n">
-        <v>6721366.78915796</v>
+        <v>6721361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1598,19 +1505,9 @@
           <t>2023-07-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1640,7 +1537,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Horizontal, dead with ground contact # Gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1658,44 +1555,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110633540</v>
+        <v>110633253</v>
       </c>
       <c r="B9" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1703,10 +1593,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484830.0636218826</v>
+        <v>484838</v>
       </c>
       <c r="R9" t="n">
-        <v>6721360.781571877</v>
+        <v>6721392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1736,19 +1626,9 @@
           <t>2023-07-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1773,12 +1653,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Gran</t>
+          <t>Standing dead tree/snags # Brandstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 8714-2026 artfynd.xlsx
+++ b/artfynd/A 8714-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110633567</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110632930</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1051,6 +1066,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110633009</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1177,6 +1197,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110633161</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1298,6 +1323,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110633238</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1429,6 +1459,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110632958</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1552,6 +1587,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110633540</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1673,8 +1713,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110633253</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>